--- a/tmp/preenchimento_materia.xlsx
+++ b/tmp/preenchimento_materia.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,26 @@
           <t>Vm2</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>longarina_g_m</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>longarina_g_v</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>longarina_g_f</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tabuleiro_g_m</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,28 +535,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41.58539580037238</v>
+        <v>43.30032901240965</v>
       </c>
       <c r="E2" t="n">
-        <v>38.77984425368555</v>
+        <v>38.59265056441485</v>
       </c>
       <c r="F2" t="n">
-        <v>5.135975027281729</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="G2" t="n">
-        <v>50.8971335744869</v>
+        <v>49.3467117491757</v>
       </c>
       <c r="H2" t="n">
-        <v>3.89643038967155</v>
+        <v>4.239455103404638</v>
       </c>
       <c r="I2" t="n">
-        <v>2.793360096413218</v>
+        <v>2.987834308316526</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1115737233033311</v>
+        <v>0.09428715733743846</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.005153496846184669</v>
+        <v>-3.249956790546093e-05</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -544,7 +564,19 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.2069155626972754</v>
+        <v>0.2213210598752982</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.01085332637437773</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.506837675082949</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.7230904993390085</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-3.249956790546093e-05</v>
       </c>
     </row>
     <row r="3">
@@ -562,28 +594,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36.1047448323258</v>
+        <v>37.771035565999</v>
       </c>
       <c r="E3" t="n">
-        <v>46.36003343303624</v>
+        <v>38.58524416734394</v>
       </c>
       <c r="F3" t="n">
-        <v>5.47424186258545</v>
+        <v>6.4441115629895</v>
       </c>
       <c r="G3" t="n">
-        <v>58.09383677841461</v>
+        <v>55.16251361059032</v>
       </c>
       <c r="H3" t="n">
-        <v>3.00578806869876</v>
+        <v>4.202465328304597</v>
       </c>
       <c r="I3" t="n">
-        <v>2.278249194072044</v>
+        <v>2.463973760303255</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1646747083330305</v>
+        <v>0.136420249671501</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0005037129726038952</v>
+        <v>-2.369586660974905e-05</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -591,7 +623,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1687591995608921</v>
+        <v>0.1825165748372782</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.005951444277281215</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.4437655910088536</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.6009717469901446</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.369586660974905e-05</v>
       </c>
     </row>
     <row r="4">
@@ -609,36 +653,48 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.7882327231521</v>
+        <v>34.50082615966561</v>
       </c>
       <c r="E4" t="n">
-        <v>39.0803974587415</v>
+        <v>39.44045839895245</v>
       </c>
       <c r="F4" t="n">
-        <v>5.012531212287101</v>
+        <v>6.053403072778151</v>
       </c>
       <c r="G4" t="n">
-        <v>60.95090466808845</v>
+        <v>59.94232120113513</v>
       </c>
       <c r="H4" t="n">
-        <v>4.112772956913566</v>
+        <v>4.915986816386344</v>
       </c>
       <c r="I4" t="n">
-        <v>1.997740930468128</v>
+        <v>2.154356729234808</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2004337360951663</v>
+        <v>0.1634369906930518</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.006290926885428757</v>
+        <v>-0.0007399133282450645</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Flexão long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1479808096643058</v>
+        <v>0.1595819799433191</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.02080470226882473</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.4217613216615316</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.524644410921533</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.0007399133282450645</v>
       </c>
     </row>
     <row r="5">
@@ -656,28 +712,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.40981315613967</v>
+        <v>31.80642995897011</v>
       </c>
       <c r="E5" t="n">
-        <v>38.77987645575738</v>
+        <v>38.57278921674467</v>
       </c>
       <c r="F5" t="n">
-        <v>6.03109023750347</v>
+        <v>5.849585006547325</v>
       </c>
       <c r="G5" t="n">
-        <v>71.34222705156091</v>
+        <v>62.82985537838879</v>
       </c>
       <c r="H5" t="n">
-        <v>2.394784524272573</v>
+        <v>2.19572770971801</v>
       </c>
       <c r="I5" t="n">
-        <v>1.817437055535568</v>
+        <v>1.902570534085073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2423987001062228</v>
+        <v>0.199184200410489</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007605167248810103</v>
+        <v>-4.49952331365542e-05</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -685,7 +741,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1346249670767087</v>
+        <v>0.1409311506729684</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-4.49952331365542e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.3983698063030873</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.4214686263568848</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.003705616751319009</v>
       </c>
     </row>
     <row r="6">
@@ -703,36 +771,48 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.61320119289024</v>
+        <v>30.1175187685287</v>
       </c>
       <c r="E6" t="n">
-        <v>33.66940640593264</v>
+        <v>38.58102384260085</v>
       </c>
       <c r="F6" t="n">
-        <v>5.163385524885169</v>
+        <v>5.568451495717177</v>
       </c>
       <c r="G6" t="n">
-        <v>66.38788569365376</v>
+        <v>64.70141556596151</v>
       </c>
       <c r="H6" t="n">
-        <v>2.947543769747156</v>
+        <v>4.99898833757351</v>
       </c>
       <c r="I6" t="n">
-        <v>1.664982179631355</v>
+        <v>1.745345866891513</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2611802847005887</v>
+        <v>0.2120987688860624</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0006819025657234315</v>
+        <v>-0.01404251871382479</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Flexão long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1233320133060263</v>
+        <v>0.129284879029001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.01701362564796432</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.4007305560416317</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.3890936780355116</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.01404251871382479</v>
       </c>
     </row>
     <row r="7">
@@ -750,28 +830,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.0565129808774</v>
+        <v>52.36706380008528</v>
       </c>
       <c r="E7" t="n">
-        <v>30.59771706263513</v>
+        <v>26.71965106636539</v>
       </c>
       <c r="F7" t="n">
-        <v>5.000010962882786</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="G7" t="n">
-        <v>62.25937300521064</v>
+        <v>32.20196361610991</v>
       </c>
       <c r="H7" t="n">
-        <v>2.344549947624847</v>
+        <v>2.838669016199924</v>
       </c>
       <c r="I7" t="n">
-        <v>4.690470938133339</v>
+        <v>5.089167025173537</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1645031433297194</v>
+        <v>0.1355154174974358</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.00205071103919296</v>
+        <v>-0.0008493821818890155</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -779,7 +859,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.2605817187851855</v>
+        <v>0.2827315013985298</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.0008493821818890155</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.5963430546182884</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.6009217979306706</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3468612123925892</v>
       </c>
     </row>
     <row r="8">
@@ -797,28 +889,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44.05652684264814</v>
+        <v>45.85402521435842</v>
       </c>
       <c r="E8" t="n">
-        <v>45.92817269145282</v>
+        <v>45.72961753363473</v>
       </c>
       <c r="F8" t="n">
-        <v>8.945332565835491</v>
+        <v>8.707857284869322</v>
       </c>
       <c r="G8" t="n">
-        <v>83.15222345921241</v>
+        <v>72.77877971798655</v>
       </c>
       <c r="H8" t="n">
-        <v>4.679416693465779</v>
+        <v>2.688695464336434</v>
       </c>
       <c r="I8" t="n">
-        <v>3.898715426182167</v>
+        <v>4.075739704689213</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2371160932477766</v>
+        <v>0.1987865873025833</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.880560150476222e-05</v>
+        <v>-7.965021909209704e-06</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -826,7 +918,19 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.2165953014545648</v>
+        <v>0.2264299835938452</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.003540843546782222</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.5427882435421428</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.4302158532863291</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-7.965021909209704e-06</v>
       </c>
     </row>
     <row r="9">
@@ -844,28 +948,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.21016628507971</v>
+        <v>43.05068280090355</v>
       </c>
       <c r="E9" t="n">
-        <v>45.92808962993951</v>
+        <v>40.00441977211329</v>
       </c>
       <c r="F9" t="n">
-        <v>8.168703619226088</v>
+        <v>8.427766118160518</v>
       </c>
       <c r="G9" t="n">
-        <v>96.03997941885335</v>
+        <v>75.64395888371739</v>
       </c>
       <c r="H9" t="n">
-        <v>4.340219083976546</v>
+        <v>4.807117777741808</v>
       </c>
       <c r="I9" t="n">
-        <v>3.366124013626187</v>
+        <v>3.694451453577154</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2850184663756352</v>
+        <v>0.2148500980899601</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001512736466339064</v>
+        <v>-0.006821511763075021</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -873,7 +977,19 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.1870068896458993</v>
+        <v>0.2052473029765086</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.09477910511405589</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.5528033414880295</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.3906945606312388</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.006821511763075021</v>
       </c>
     </row>
     <row r="10">
@@ -891,28 +1007,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36.98088601252041</v>
+        <v>38.70800876656642</v>
       </c>
       <c r="E10" t="n">
-        <v>45.92566615819528</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="F10" t="n">
-        <v>7.600636194497569</v>
+        <v>5.038503516121577</v>
       </c>
       <c r="G10" t="n">
-        <v>108.2328819144914</v>
+        <v>54.90409830079034</v>
       </c>
       <c r="H10" t="n">
-        <v>4.837563399065901</v>
+        <v>4.80995185845303</v>
       </c>
       <c r="I10" t="n">
-        <v>2.961284512506006</v>
+        <v>3.162802575286086</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3508094557375172</v>
+        <v>0.2774970225805606</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0003709822406749976</v>
+        <v>-0.0003091151523873324</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -920,7 +1036,19 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.1645158062503337</v>
+        <v>0.1757112541825603</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.009249881968349308</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.5064945972664899</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1882271410107352</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0003091151523873324</v>
       </c>
     </row>
     <row r="11">
@@ -938,36 +1066,48 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34.84153929307306</v>
+        <v>36.46761472783696</v>
       </c>
       <c r="E11" t="n">
-        <v>40.76589219078036</v>
+        <v>45.64889896822883</v>
       </c>
       <c r="F11" t="n">
-        <v>7.553447585497219</v>
+        <v>7.14120115821786</v>
       </c>
       <c r="G11" t="n">
-        <v>114.4798639939993</v>
+        <v>112.0466026805547</v>
       </c>
       <c r="H11" t="n">
-        <v>3.530276020700602</v>
+        <v>4.085343527492916</v>
       </c>
       <c r="I11" t="n">
-        <v>2.760082041630822</v>
+        <v>2.844741888799267</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3828180862558426</v>
+        <v>0.3131998549984799</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0008745344714838011</v>
+        <v>-0.0003855082596174151</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Flexão long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.1533378912017123</v>
+        <v>0.1580412160444037</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.0005089974318245905</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.4952952494265003</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.1103176749524275</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.0003855082596174151</v>
       </c>
     </row>
     <row r="12">
@@ -985,36 +1125,48 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57.55909872872024</v>
+        <v>60.12895816616369</v>
       </c>
       <c r="E12" t="n">
-        <v>47.69253028991933</v>
+        <v>45.50845183236608</v>
       </c>
       <c r="F12" t="n">
-        <v>8.256063745951991</v>
+        <v>8.065365997005481</v>
       </c>
       <c r="G12" t="n">
-        <v>62.19281260660543</v>
+        <v>54.31680724392184</v>
       </c>
       <c r="H12" t="n">
-        <v>2.014534985465771</v>
+        <v>4.233200320833652</v>
       </c>
       <c r="I12" t="n">
-        <v>6.933241039211455</v>
+        <v>7.330891380711732</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1908845395863809</v>
+        <v>0.1584657101904744</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0008702578513717618</v>
+        <v>-0.0004839325493377498</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Flexão tab.</t>
+          <t>Flexão long.</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3081440461871758</v>
+        <v>0.3258173946982992</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.0004839325493377498</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.6121444124867106</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.5517558592259413</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.006026175317353261</v>
       </c>
     </row>
     <row r="13">
@@ -1032,36 +1184,48 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50.23680961639727</v>
+        <v>52.54924801142197</v>
       </c>
       <c r="E13" t="n">
-        <v>47.51991893794252</v>
+        <v>40.91108781728804</v>
       </c>
       <c r="F13" t="n">
-        <v>7.982316828459679</v>
+        <v>8.214539252137214</v>
       </c>
       <c r="G13" t="n">
-        <v>96.45682370281686</v>
+        <v>63.90138737133831</v>
       </c>
       <c r="H13" t="n">
-        <v>3.320384491223975</v>
+        <v>3.192062454640019</v>
       </c>
       <c r="I13" t="n">
-        <v>5.605060828850484</v>
+        <v>6.00115923478459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2757334625624173</v>
+        <v>0.2276951490223749</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.197328497221637e-05</v>
+        <v>-0.000147077710456836</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Flexão long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.2491138146155771</v>
+        <v>0.2667181882126485</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.001052684534744121</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.5695650302909228</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.358978541816616</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.000147077710456836</v>
       </c>
     </row>
     <row r="14">
@@ -1079,28 +1243,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.68550834238653</v>
+        <v>47.78249191992249</v>
       </c>
       <c r="E14" t="n">
-        <v>46.49148091850952</v>
+        <v>45.5055607943091</v>
       </c>
       <c r="F14" t="n">
-        <v>7.518886875296761</v>
+        <v>7.34146072476878</v>
       </c>
       <c r="G14" t="n">
-        <v>107.1568482923698</v>
+        <v>69.97719751561638</v>
       </c>
       <c r="H14" t="n">
-        <v>4.962435909842737</v>
+        <v>2.24145829332547</v>
       </c>
       <c r="I14" t="n">
-        <v>4.82587120227698</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3362535804521588</v>
+        <v>0.2772469806530269</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.09949909895215e-05</v>
+        <v>-0.001803562843051572</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1108,7 +1272,19 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2144831645456436</v>
+        <v>0.2262105510299955</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.002524319584938742</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.5505750780822475</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.2228081440103832</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.001803562843051572</v>
       </c>
     </row>
     <row r="15">
@@ -1126,28 +1302,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42.40177907096175</v>
+        <v>44.4903616706851</v>
       </c>
       <c r="E15" t="n">
-        <v>47.71884366769421</v>
+        <v>45.50040576736203</v>
       </c>
       <c r="F15" t="n">
-        <v>6.964431857324951</v>
+        <v>10.89259364722904</v>
       </c>
       <c r="G15" t="n">
-        <v>115.0476357447716</v>
+        <v>125.1650263522084</v>
       </c>
       <c r="H15" t="n">
-        <v>3.028704243703436</v>
+        <v>4.608832361491563</v>
       </c>
       <c r="I15" t="n">
-        <v>4.261493190313614</v>
+        <v>4.562195032539481</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3991517605122522</v>
+        <v>0.3543055275736025</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.954205581189098e-05</v>
+        <v>-0.0004255891008984285</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1155,7 +1331,19 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.1893996973472717</v>
+        <v>0.2027642236684214</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.0004255891008984285</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.5396387706512332</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.07501491866105987</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.001255009107871026</v>
       </c>
     </row>
     <row r="16">
@@ -1173,36 +1361,48 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40.26963656156759</v>
+        <v>41.78910698341235</v>
       </c>
       <c r="E16" t="n">
-        <v>47.49361926720055</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="F16" t="n">
-        <v>10.01074886377354</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="G16" t="n">
-        <v>153.6114416604304</v>
+        <v>78.07177320186793</v>
       </c>
       <c r="H16" t="n">
-        <v>2.910196358277848</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="I16" t="n">
-        <v>3.989492743182196</v>
+        <v>4.08401858099314</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4626662549072069</v>
+        <v>0.3580501558917902</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.990956752765508e-05</v>
+        <v>-0.001135419239060512</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Flecha long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.1773107885858754</v>
+        <v>0.1815119369330284</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.003242188247305976</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.5393256727140772</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.007913572433008303</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.001135419239060512</v>
       </c>
     </row>
     <row r="17">
@@ -1220,28 +1420,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.43523565859909</v>
+        <v>66.72204180882061</v>
       </c>
       <c r="E17" t="n">
-        <v>48.78422229089842</v>
+        <v>45.41746335793211</v>
       </c>
       <c r="F17" t="n">
-        <v>7.100137676392178</v>
+        <v>6.469494530974315</v>
       </c>
       <c r="G17" t="n">
-        <v>82.86316683108906</v>
+        <v>38.08377189014391</v>
       </c>
       <c r="H17" t="n">
-        <v>2.716724633791615</v>
+        <v>2.10992173247367</v>
       </c>
       <c r="I17" t="n">
-        <v>9.313027057873045</v>
+        <v>9.978174847141487</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2145231243156965</v>
+        <v>0.1739721108204294</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.7572627877126e-05</v>
+        <v>-0.0001516477460967912</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1249,7 +1449,19 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.344926928069372</v>
+        <v>0.3695620313756106</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.01693674328383978</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.6369903004766894</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.5206527984196355</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.0001516477460967912</v>
       </c>
     </row>
     <row r="18">
@@ -1267,28 +1479,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55.75718741284847</v>
+        <v>58.16936864108953</v>
       </c>
       <c r="E18" t="n">
-        <v>49.0310671394415</v>
+        <v>45.42231645021892</v>
       </c>
       <c r="F18" t="n">
-        <v>12.50609466930299</v>
+        <v>12.73550107390722</v>
       </c>
       <c r="G18" t="n">
-        <v>168.9818750251465</v>
+        <v>106.8650710207591</v>
       </c>
       <c r="H18" t="n">
-        <v>2.208715832970053</v>
+        <v>4.841317111729771</v>
       </c>
       <c r="I18" t="n">
-        <v>7.51079224502173</v>
+        <v>7.907328652079627</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3257358813324761</v>
+        <v>0.2717713983098701</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.000732344004297e-05</v>
+        <v>-0.001544738293483415</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1296,7 +1508,19 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.2781774905563604</v>
+        <v>0.2928640241510973</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.001544738293483415</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.5949754526708404</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.2980087715114788</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.002627528927827589</v>
       </c>
     </row>
     <row r="19">
@@ -1314,36 +1538,48 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50.71096070558761</v>
+        <v>52.89201311789211</v>
       </c>
       <c r="E19" t="n">
-        <v>49.30554835286635</v>
+        <v>45.4205450746652</v>
       </c>
       <c r="F19" t="n">
-        <v>11.21483456612283</v>
+        <v>11.48075322454395</v>
       </c>
       <c r="G19" t="n">
-        <v>166.9809240929542</v>
+        <v>114.2061005784972</v>
       </c>
       <c r="H19" t="n">
-        <v>4.562006623444558</v>
+        <v>4.955868441350977</v>
       </c>
       <c r="I19" t="n">
-        <v>6.439473971248886</v>
+        <v>6.770859590773329</v>
       </c>
       <c r="J19" t="n">
-        <v>0.399148028140201</v>
+        <v>0.3333454842982386</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0001224329744813115</v>
+        <v>-0.0003028635709031783</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Flexão long.</t>
+          <t>Flexão tab.</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.238499035972181</v>
+        <v>0.2507725774360492</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.00183061124163492</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.5792389477886857</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.1473015012360963</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.0003028635709031783</v>
       </c>
     </row>
     <row r="20">
@@ -1361,28 +1597,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.29756891491404</v>
+        <v>49.24175979582745</v>
       </c>
       <c r="E20" t="n">
-        <v>48.78143490094609</v>
+        <v>45.42603699289726</v>
       </c>
       <c r="F20" t="n">
-        <v>10.33042855809284</v>
+        <v>10.54809805488446</v>
       </c>
       <c r="G20" t="n">
-        <v>134.1225766203304</v>
+        <v>119.4426269482659</v>
       </c>
       <c r="H20" t="n">
-        <v>3.19283784578212</v>
+        <v>2.447699023964044</v>
       </c>
       <c r="I20" t="n">
-        <v>5.734245309541487</v>
+        <v>6.015365616621969</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4666601237689672</v>
+        <v>0.3924347892092494</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0002660652267048286</v>
+        <v>-0.0007606489692424372</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1390,7 +1626,19 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.212379455908944</v>
+        <v>0.222791319134147</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.009437309486892665</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.5755171435942383</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.0009898024718170012</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.0007606489692424372</v>
       </c>
     </row>
     <row r="21">
@@ -1408,28 +1656,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.46294694412061</v>
+        <v>47.59972549193003</v>
       </c>
       <c r="E21" t="n">
-        <v>48.78068953429131</v>
+        <v>45.4357535808355</v>
       </c>
       <c r="F21" t="n">
-        <v>9.550076688722122</v>
+        <v>9.898274078037646</v>
       </c>
       <c r="G21" t="n">
-        <v>179.7022969785597</v>
+        <v>172.1399104202384</v>
       </c>
       <c r="H21" t="n">
-        <v>2.900956847144865</v>
+        <v>2.526091602190318</v>
       </c>
       <c r="I21" t="n">
-        <v>5.299371811680241</v>
+        <v>5.631677718249779</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4741233527125679</v>
+        <v>0.3914046376228014</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.537930701663205e-05</v>
+        <v>-1.287354696606363e-05</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1437,7 +1685,19 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.1962730300622312</v>
+        <v>0.2085806562314733</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.06735794575260122</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.5896527409102807</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.000296229902751674</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.287354696606363e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1523,2052 +1783,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45.68550834238653</v>
+        <v>47.78249191992249</v>
       </c>
       <c r="B2" t="n">
-        <v>107.1568482923698</v>
+        <v>69.97719751561638</v>
       </c>
       <c r="C2" t="n">
-        <v>46.49148091850952</v>
+        <v>45.5055607943091</v>
       </c>
       <c r="D2" t="n">
-        <v>7.518886875296761</v>
+        <v>7.34146072476878</v>
       </c>
       <c r="E2" t="n">
-        <v>4.962435909842737</v>
+        <v>2.24145829332547</v>
       </c>
       <c r="F2" t="n">
-        <v>4.82587120227698</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3362535804521588</v>
+        <v>0.2772469806530269</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.001194260096629835</v>
+        <v>-0.002524319584938742</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5495845472421893</v>
+        <v>-0.5505750780822475</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2194527560181604</v>
+        <v>-0.2228081440103832</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.09949909895215e-05</v>
+        <v>-0.001803562843051572</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5533546070803549</v>
+        <v>-0.5685499461328165</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04476082411959584</v>
+        <v>-0.001235732068689266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45.68550834238653</v>
+        <v>47.78249191992249</v>
       </c>
       <c r="B3" t="n">
-        <v>107.1568482923698</v>
+        <v>69.97719751561638</v>
       </c>
       <c r="C3" t="n">
-        <v>46.49148091850952</v>
+        <v>45.5055607943091</v>
       </c>
       <c r="D3" t="n">
-        <v>7.518886875296761</v>
+        <v>7.34146072476878</v>
       </c>
       <c r="E3" t="n">
-        <v>4.962490888165513</v>
+        <v>2.203804983998379</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82587120227698</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3362535804521588</v>
+        <v>0.2772469806530269</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001194260096629835</v>
+        <v>-0.002524319584938742</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5495845472421893</v>
+        <v>-0.5505750780822475</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2194527560181604</v>
+        <v>-0.2228081440103832</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.09949909895215e-05</v>
+        <v>-0.001803562843051572</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5533546070803549</v>
+        <v>-0.5685499461328165</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04476082411959584</v>
+        <v>-0.001235732068689266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>45.86240373007536</v>
+        <v>47.81234225732649</v>
       </c>
       <c r="B4" t="n">
-        <v>94.43335656987762</v>
+        <v>69.72708735945707</v>
       </c>
       <c r="C4" t="n">
-        <v>47.15973038567474</v>
+        <v>45.50300986032286</v>
       </c>
       <c r="D4" t="n">
-        <v>7.518886875296761</v>
+        <v>7.334308487558927</v>
       </c>
       <c r="E4" t="n">
-        <v>3.942266596540438</v>
+        <v>3.878739551263629</v>
       </c>
       <c r="F4" t="n">
-        <v>4.86834892624312</v>
+        <v>5.092670933710119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3315247091474395</v>
+        <v>0.2765821859928763</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0124343338248406</v>
+        <v>-0.004370009143217606</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5534912218943874</v>
+        <v>-0.5512194782458717</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2310853219297175</v>
+        <v>-0.2247204411623624</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01935107742010246</v>
+        <v>-0.0007672042755773163</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5545292034189687</v>
+        <v>-0.5687489483821766</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05185684548528968</v>
+        <v>-0.0006688578495246678</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>46.32514612472548</v>
+        <v>48.39503363492054</v>
       </c>
       <c r="B5" t="n">
-        <v>98.81401774508782</v>
+        <v>68.79730484758848</v>
       </c>
       <c r="C5" t="n">
-        <v>46.4942875405067</v>
+        <v>45.50303972166795</v>
       </c>
       <c r="D5" t="n">
-        <v>7.458401525270575</v>
+        <v>7.281223700384093</v>
       </c>
       <c r="E5" t="n">
-        <v>3.461992390335244</v>
+        <v>4.704434380421534</v>
       </c>
       <c r="F5" t="n">
-        <v>4.90509251318634</v>
+        <v>5.16985968158542</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3188549281136459</v>
+        <v>0.2641506759424748</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04148929937278052</v>
+        <v>-0.03942181727171946</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5637271273349747</v>
+        <v>-0.5635097204968957</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2610496621901416</v>
+        <v>-0.2607964770085074</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.003329367354169368</v>
+        <v>-0.005259663590506306</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5576018416012231</v>
+        <v>-0.572633557566137</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04485430263479391</v>
+        <v>-0.0006754937039880893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46.58206828514303</v>
+        <v>48.77794009849785</v>
       </c>
       <c r="B6" t="n">
-        <v>107.1568482923698</v>
+        <v>69.42273841714417</v>
       </c>
       <c r="C6" t="n">
-        <v>46.49137732886422</v>
+        <v>45.50324500119541</v>
       </c>
       <c r="D6" t="n">
-        <v>7.44051545109255</v>
+        <v>7.281868996020895</v>
       </c>
       <c r="E6" t="n">
-        <v>4.878184924497247</v>
+        <v>4.668125699560026</v>
       </c>
       <c r="F6" t="n">
-        <v>4.938476453033427</v>
+        <v>5.22844498200455</v>
       </c>
       <c r="G6" t="n">
-        <v>0.312204989296181</v>
+        <v>0.2564253171827088</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05705050958351335</v>
+        <v>-0.06152752534112608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5692321630579149</v>
+        <v>-0.5713210360476737</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2769587037287831</v>
+        <v>-0.2833200247700985</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.006337690023705479</v>
+        <v>-0.01798310028979123</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5593078206709883</v>
+        <v>-0.575186267323319</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04475737391994564</v>
+        <v>-0.000721111376758149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47.18270609210895</v>
+        <v>48.9505455726445</v>
       </c>
       <c r="B7" t="n">
-        <v>102.8248798964181</v>
+        <v>69.42273841714417</v>
       </c>
       <c r="C7" t="n">
-        <v>46.49126062508712</v>
+        <v>45.50324531434479</v>
       </c>
       <c r="D7" t="n">
-        <v>7.388089819404933</v>
+        <v>7.258060547423</v>
       </c>
       <c r="E7" t="n">
-        <v>4.396663436033148</v>
+        <v>4.668125699560026</v>
       </c>
       <c r="F7" t="n">
-        <v>5.015331791798237</v>
+        <v>5.250066797957754</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2973266543362237</v>
+        <v>0.2530044121053108</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09213453603293716</v>
+        <v>-0.07128552104153574</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5817405647692222</v>
+        <v>-0.5747886889445063</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3125090048358715</v>
+        <v>-0.293210638819654</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01084306253123177</v>
+        <v>-0.01723141174487232</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5632960929380761</v>
+        <v>-0.5763369704842967</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04475348693558761</v>
+        <v>-0.0007211809655077728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.73477360559138</v>
+        <v>49.89019626925267</v>
       </c>
       <c r="B8" t="n">
-        <v>109.0649661389219</v>
+        <v>69.30302237219834</v>
       </c>
       <c r="C8" t="n">
-        <v>46.50052962996664</v>
+        <v>45.50304080289227</v>
       </c>
       <c r="D8" t="n">
-        <v>7.31850951336084</v>
+        <v>7.281223700384093</v>
       </c>
       <c r="E8" t="n">
-        <v>4.809936133734454</v>
+        <v>4.758056967155396</v>
       </c>
       <c r="F8" t="n">
-        <v>5.082801812421944</v>
+        <v>5.400692012265928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2844170465197531</v>
+        <v>0.2355827985466945</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1228673599668328</v>
+        <v>-0.1219714841635738</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5928135422566122</v>
+        <v>-0.5929500368265942</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3432829107650937</v>
+        <v>-0.3440048400198346</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.009627874225848959</v>
+        <v>-0.01338197204094748</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5669618554459416</v>
+        <v>-0.5742862757501423</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04506220425283802</v>
+        <v>-0.0006757339760589398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48.09181442479746</v>
+        <v>50.32087980571383</v>
       </c>
       <c r="B9" t="n">
-        <v>99.97462982633684</v>
+        <v>69.72708735945707</v>
       </c>
       <c r="C9" t="n">
-        <v>43.81358086122183</v>
+        <v>45.54632931926534</v>
       </c>
       <c r="D9" t="n">
-        <v>7.489606421615106</v>
+        <v>7.334308487558927</v>
       </c>
       <c r="E9" t="n">
-        <v>3.934041604359732</v>
+        <v>4.721906942309611</v>
       </c>
       <c r="F9" t="n">
-        <v>5.183123022073831</v>
+        <v>5.480784967905448</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2768815854383907</v>
+        <v>0.2281800276170181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1417119858091947</v>
+        <v>-0.1402747792677228</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5996040449163185</v>
+        <v>-0.598906839774798</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3619205231837545</v>
+        <v>-0.3613621781627853</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.007938616274420886</v>
+        <v>-0.001468657600373793</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5693326286156345</v>
+        <v>-0.5686989054361875</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06630490289211692</v>
+        <v>-0.01029540428118661</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48.81625997050701</v>
+        <v>51.01069393298776</v>
       </c>
       <c r="B10" t="n">
-        <v>81.13807912263638</v>
+        <v>67.88963642368088</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54437980852438</v>
+        <v>45.50344070249509</v>
       </c>
       <c r="D10" t="n">
-        <v>7.082025335307063</v>
+        <v>7.258060547423</v>
       </c>
       <c r="E10" t="n">
-        <v>4.776013413088482</v>
+        <v>4.732403003412849</v>
       </c>
       <c r="F10" t="n">
-        <v>5.19808081535891</v>
+        <v>5.573555095483558</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2610087097789561</v>
+        <v>0.2167320088158744</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1792222111876859</v>
+        <v>-0.1776801788962808</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6134229767222383</v>
+        <v>-0.6132598069477108</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3988033272265631</v>
+        <v>-0.3987278966989371</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.001325462222529007</v>
+        <v>-0.04311363348973458</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5741429919418523</v>
+        <v>-0.5815695105644205</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0298856128699841</v>
+        <v>-0.0007646005544650891</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49.22203693253917</v>
+        <v>51.06996924949777</v>
       </c>
       <c r="B11" t="n">
-        <v>97.71043870825557</v>
+        <v>69.42273841714417</v>
       </c>
       <c r="C11" t="n">
-        <v>47.60403004142217</v>
+        <v>45.50324531434479</v>
       </c>
       <c r="D11" t="n">
-        <v>7.048168144837357</v>
+        <v>7.258060547423</v>
       </c>
       <c r="E11" t="n">
-        <v>4.690930938483111</v>
+        <v>4.732403003412849</v>
       </c>
       <c r="F11" t="n">
-        <v>5.25487552501313</v>
+        <v>5.583053388205696</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2529622334716599</v>
+        <v>0.2157917488652142</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1990435264106463</v>
+        <v>-0.1770385772451256</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6207532345709803</v>
+        <v>-0.6123799769303551</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4180234095164779</v>
+        <v>-0.3974122318271481</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.006485839169360465</v>
+        <v>-0.00291913003173805</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5768373761206821</v>
+        <v>-0.5734431385801526</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02753003240461939</v>
+        <v>-0.0007211809655077728</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>49.55202337136529</v>
+        <v>51.68077834691471</v>
       </c>
       <c r="B12" t="n">
-        <v>97.30772337084079</v>
+        <v>68.82004364910256</v>
       </c>
       <c r="C12" t="n">
-        <v>46.51966061505168</v>
+        <v>45.50449743210885</v>
       </c>
       <c r="D12" t="n">
-        <v>7.069895682774661</v>
+        <v>7.270264402448737</v>
       </c>
       <c r="E12" t="n">
-        <v>4.678263825834765</v>
+        <v>2.465507580788703</v>
       </c>
       <c r="F12" t="n">
-        <v>5.307110394460247</v>
+        <v>5.684178162102763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2467001370834926</v>
+        <v>0.2064191380622778</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2146582775144348</v>
+        <v>-0.2053833228674357</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6265582589351355</v>
+        <v>-0.6228678016871988</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.433046929458129</v>
+        <v>-0.424830153057174</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0008242509450980656</v>
+        <v>-0.0253534287377108</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5790285065277628</v>
+        <v>-0.5773115961971265</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04569938876925415</v>
+        <v>-0.0009994293575228685</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50.391413930841</v>
+        <v>52.30736135969952</v>
       </c>
       <c r="B13" t="n">
-        <v>78.39587003593816</v>
+        <v>69.97719751561638</v>
       </c>
       <c r="C13" t="n">
-        <v>48.06438439191874</v>
+        <v>45.5055607943091</v>
       </c>
       <c r="D13" t="n">
-        <v>6.872649168629714</v>
+        <v>7.273509936592633</v>
       </c>
       <c r="E13" t="n">
-        <v>4.756349812651063</v>
+        <v>2.203804983998379</v>
       </c>
       <c r="F13" t="n">
-        <v>5.408713219595454</v>
+        <v>5.787226248956779</v>
       </c>
       <c r="G13" t="n">
-        <v>0.23142922768612</v>
+        <v>0.1973385318160244</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2527203977953458</v>
+        <v>-0.2331146027031654</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6408730715787432</v>
+        <v>-0.6332315622768143</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4692858347708943</v>
+        <v>-0.451344991352949</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.005671098582445858</v>
+        <v>-0.04578601733495875</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5846021118699293</v>
+        <v>-0.5812799552780969</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01091609527235446</v>
+        <v>-0.001235732068689266</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50.68916192663898</v>
+        <v>54.19834248498943</v>
       </c>
       <c r="B14" t="n">
-        <v>68.88035789551205</v>
+        <v>111.6009360480608</v>
       </c>
       <c r="C14" t="n">
-        <v>47.64776893635629</v>
+        <v>45.5003755621402</v>
       </c>
       <c r="D14" t="n">
-        <v>6.849195236134003</v>
+        <v>11.3841681992671</v>
       </c>
       <c r="E14" t="n">
-        <v>4.008270460250317</v>
+        <v>2.618149732209953</v>
       </c>
       <c r="F14" t="n">
-        <v>5.504661959749718</v>
+        <v>5.791541598519238</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2259744193595425</v>
+        <v>0.185969473565786</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2658483259695592</v>
+        <v>-0.305977102790037</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.645896106263751</v>
+        <v>-0.6603072373481338</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4816975354233231</v>
+        <v>-0.5188788430022415</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0626529906233777</v>
+        <v>-0.004884579771750142</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5969389838698105</v>
+        <v>-0.2814875686374207</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02580278874640916</v>
+        <v>-8.345825337846557e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>51.6817812659734</v>
+        <v>55.38485388997032</v>
       </c>
       <c r="B15" t="n">
-        <v>97.74219934088008</v>
+        <v>109.7288188162734</v>
       </c>
       <c r="C15" t="n">
-        <v>46.47290161539303</v>
+        <v>45.50574547822254</v>
       </c>
       <c r="D15" t="n">
-        <v>6.848400561949573</v>
+        <v>11.29717688383059</v>
       </c>
       <c r="E15" t="n">
-        <v>4.694306905961339</v>
+        <v>2.261618701926519</v>
       </c>
       <c r="F15" t="n">
-        <v>5.595534995733906</v>
+        <v>5.92718119273421</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2104180825968835</v>
+        <v>0.1713289496766063</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.30641032013677</v>
+        <v>-0.348938363909624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6613917427390555</v>
+        <v>-0.6770878142175932</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5193437617634087</v>
+        <v>-0.5580511436445196</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01109178609542102</v>
+        <v>-0.007923990259174235</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5931702309549749</v>
+        <v>-0.2903864041747775</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.04414201415142111</v>
+        <v>-0.001276772938343107</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52.52613193660601</v>
+        <v>55.38485388997032</v>
       </c>
       <c r="B16" t="n">
-        <v>86.59745500733307</v>
+        <v>110.3866662044174</v>
       </c>
       <c r="C16" t="n">
-        <v>47.6919448963091</v>
+        <v>45.50574547822254</v>
       </c>
       <c r="D16" t="n">
-        <v>6.647560093136355</v>
+        <v>11.29717688383059</v>
       </c>
       <c r="E16" t="n">
-        <v>4.048577218581604</v>
+        <v>2.261618701926519</v>
       </c>
       <c r="F16" t="n">
-        <v>5.692956580952115</v>
+        <v>5.92718119273421</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1978547066081582</v>
+        <v>0.1713289496766063</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3388532835644504</v>
+        <v>-0.348938363909624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6740228468610012</v>
+        <v>-0.6770878142175932</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5490016171115389</v>
+        <v>-0.5580511436445196</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.008781266398436894</v>
+        <v>-0.007923990259174235</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5987767717426615</v>
+        <v>-0.2903864041747775</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.02463121687668946</v>
+        <v>-0.001276772938343107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52.66003666132309</v>
+        <v>56.34833825090419</v>
       </c>
       <c r="B17" t="n">
-        <v>94.34795088003276</v>
+        <v>111.5096021407366</v>
       </c>
       <c r="C17" t="n">
-        <v>46.45559955148651</v>
+        <v>45.50359008938687</v>
       </c>
       <c r="D17" t="n">
-        <v>7.506005461277271</v>
+        <v>11.29328084256004</v>
       </c>
       <c r="E17" t="n">
-        <v>4.527177760436526</v>
+        <v>4.680650490889004</v>
       </c>
       <c r="F17" t="n">
-        <v>5.896537437965975</v>
+        <v>6.053099759784915</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1969034009153873</v>
+        <v>0.1606141682980277</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3431154692810864</v>
+        <v>-0.3811714372044274</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6755529011198276</v>
+        <v>-0.689867648237059</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.552735289903527</v>
+        <v>-0.5868787739906941</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2056376142813431</v>
+        <v>-0.0003377442414778973</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5996659074144883</v>
+        <v>-0.2870472234597369</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.04374327270933765</v>
+        <v>-0.0007977976415256272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53.82005681036627</v>
+        <v>56.40621418030903</v>
       </c>
       <c r="B18" t="n">
-        <v>96.90565054654836</v>
+        <v>110.5443504241964</v>
       </c>
       <c r="C18" t="n">
-        <v>46.45559955148651</v>
+        <v>45.50304945806009</v>
       </c>
       <c r="D18" t="n">
-        <v>6.659960253266263</v>
+        <v>11.29339596053552</v>
       </c>
       <c r="E18" t="n">
-        <v>4.527177760436526</v>
+        <v>4.685117244290404</v>
       </c>
       <c r="F18" t="n">
-        <v>5.911884437455</v>
+        <v>6.060783853993888</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1807387035947317</v>
+        <v>0.1599990478994189</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3844780363155318</v>
+        <v>-0.3830380685978745</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.692029193955135</v>
+        <v>-0.6906131851572398</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5898527106251003</v>
+        <v>-0.5885332326603236</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03568628546912993</v>
+        <v>-0.001215433678404249</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6073685131047001</v>
+        <v>-0.2874704411935097</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.04374327270933765</v>
+        <v>-0.0006776573466871216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54.39477200203734</v>
+        <v>57.44879480829545</v>
       </c>
       <c r="B19" t="n">
-        <v>98.58739242447032</v>
+        <v>107.466797852891</v>
       </c>
       <c r="C19" t="n">
-        <v>46.47290161539303</v>
+        <v>45.92805886959007</v>
       </c>
       <c r="D19" t="n">
-        <v>6.848400561949573</v>
+        <v>11.02078652241831</v>
       </c>
       <c r="E19" t="n">
-        <v>4.685461668315596</v>
+        <v>4.954173294988751</v>
       </c>
       <c r="F19" t="n">
-        <v>6.044268734964364</v>
+        <v>6.165884760438061</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1738967240287157</v>
+        <v>0.1492182884393877</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4032717548787642</v>
+        <v>-0.415504495961686</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6995280824961924</v>
+        <v>-0.7037042571022523</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6063770518878031</v>
+        <v>-0.6170601123506486</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1090385101113757</v>
+        <v>-0.0002203770099821061</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6111846575994904</v>
+        <v>-0.3058659610622159</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.04414201415142111</v>
+        <v>-0.09512419324223767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56.78923106398889</v>
+        <v>57.67782240941226</v>
       </c>
       <c r="B20" t="n">
-        <v>191.253021845652</v>
+        <v>107.2625132675269</v>
       </c>
       <c r="C20" t="n">
-        <v>46.47862463816547</v>
+        <v>45.92156925335695</v>
       </c>
       <c r="D20" t="n">
-        <v>11.21673839166305</v>
+        <v>11.02078652241831</v>
       </c>
       <c r="E20" t="n">
-        <v>4.869583582464983</v>
+        <v>4.919148085721103</v>
       </c>
       <c r="F20" t="n">
-        <v>6.115108552189952</v>
+        <v>6.196626011232329</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1594846492759084</v>
+        <v>0.1470209568791762</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4652860184979328</v>
+        <v>-0.422302464885068</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7227969335081991</v>
+        <v>-0.7064650022800658</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6582745706285112</v>
+        <v>-0.6229640035795364</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.03277440515521574</v>
+        <v>-0.003750066226140183</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2992195159576923</v>
+        <v>-0.3075836680705919</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.04433262751928921</v>
+        <v>-0.09368205630154322</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56.93933244122085</v>
+        <v>59.10827631310298</v>
       </c>
       <c r="B21" t="n">
-        <v>194.1070574413548</v>
+        <v>115.0463525289678</v>
       </c>
       <c r="C21" t="n">
-        <v>46.47576575348777</v>
+        <v>45.86114893329594</v>
       </c>
       <c r="D21" t="n">
-        <v>11.31473854040148</v>
+        <v>11.17856078616011</v>
       </c>
       <c r="E21" t="n">
-        <v>4.870424522675046</v>
+        <v>2.276673664796341</v>
       </c>
       <c r="F21" t="n">
-        <v>6.155402623944119</v>
+        <v>6.422999789830811</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1580496071325</v>
+        <v>0.1343783009342897</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4693139986542189</v>
+        <v>-0.4559675357528996</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7244535698225064</v>
+        <v>-0.7187982385024314</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6616732231773834</v>
+        <v>-0.650799433718893</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05159654852148039</v>
+        <v>-0.006554178848577192</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.300340783712175</v>
+        <v>-0.2961464687308587</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.04423740832159816</v>
+        <v>-0.0802553185102102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>58.15305447305496</v>
+        <v>59.10827631310298</v>
       </c>
       <c r="B22" t="n">
-        <v>193.9102005500544</v>
+        <v>108.7118926136191</v>
       </c>
       <c r="C22" t="n">
-        <v>47.67116790999652</v>
+        <v>45.86114893329594</v>
       </c>
       <c r="D22" t="n">
-        <v>10.77756705778146</v>
+        <v>11.17856078616011</v>
       </c>
       <c r="E22" t="n">
-        <v>4.657561698956198</v>
+        <v>2.279008704046059</v>
       </c>
       <c r="F22" t="n">
-        <v>6.208952276616161</v>
+        <v>6.422999789830811</v>
       </c>
       <c r="G22" t="n">
-        <v>0.145440751990815</v>
+        <v>0.1343783009342897</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5017073731463308</v>
+        <v>-0.4559675357528996</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7382167192322001</v>
+        <v>-0.7187982385024314</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6889046330972165</v>
+        <v>-0.650799433718893</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.000537442821357156</v>
+        <v>-0.006554178848577192</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3094073719227407</v>
+        <v>-0.2961464687308587</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.02489559107381765</v>
+        <v>-0.0802553185102102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58.35090775162612</v>
+        <v>60.68563103069604</v>
       </c>
       <c r="B23" t="n">
-        <v>194.1070574413548</v>
+        <v>120.7205055283645</v>
       </c>
       <c r="C23" t="n">
-        <v>47.48430466069155</v>
+        <v>45.50362723405295</v>
       </c>
       <c r="D23" t="n">
-        <v>11.11502520284247</v>
+        <v>11.06961726733308</v>
       </c>
       <c r="E23" t="n">
-        <v>4.876776220693966</v>
+        <v>4.871589254605217</v>
       </c>
       <c r="F23" t="n">
-        <v>6.313169049045154</v>
+        <v>6.605317517287915</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1440613777774193</v>
+        <v>0.1217000744210486</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5062876708943205</v>
+        <v>-0.4966549962411677</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7400784457215618</v>
+        <v>-0.7359036744604055</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6926397271891428</v>
+        <v>-0.6850820211865416</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.05944630246475393</v>
+        <v>-0.003109634475078008</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3108853497099646</v>
+        <v>-0.3073851210937093</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.03175470305065788</v>
+        <v>-0.0008060520117678105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59.25756808020209</v>
+        <v>61.23991349509762</v>
       </c>
       <c r="B24" t="n">
-        <v>193.9102005500544</v>
+        <v>105.399957368815</v>
       </c>
       <c r="C24" t="n">
-        <v>47.67116790999652</v>
+        <v>45.52253225502457</v>
       </c>
       <c r="D24" t="n">
-        <v>10.81709492653446</v>
+        <v>11.38901618250408</v>
       </c>
       <c r="E24" t="n">
-        <v>4.63568704597812</v>
+        <v>4.45520989253854</v>
       </c>
       <c r="F24" t="n">
-        <v>6.368875923487805</v>
+        <v>6.751305767011877</v>
       </c>
       <c r="G24" t="n">
-        <v>0.135660358911808</v>
+        <v>0.1179778358930476</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5284259121088644</v>
+        <v>-0.5096014649812554</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7496335319932412</v>
+        <v>-0.741335071648861</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7108522695556688</v>
+        <v>-0.695745669868717</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.02543168690869665</v>
+        <v>-0.06644597162294989</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3176581655857978</v>
+        <v>-0.3113343836525706</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02489559107381765</v>
+        <v>-0.005007167783237926</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>59.75513530931094</v>
+        <v>62.35042780412309</v>
       </c>
       <c r="B25" t="n">
-        <v>192.5432508544934</v>
+        <v>99.47874623289547</v>
       </c>
       <c r="C25" t="n">
-        <v>47.67116790999652</v>
+        <v>45.96751496935519</v>
       </c>
       <c r="D25" t="n">
-        <v>10.64297384312006</v>
+        <v>10.66826994498174</v>
       </c>
       <c r="E25" t="n">
-        <v>4.689599333614571</v>
+        <v>4.531432214165003</v>
       </c>
       <c r="F25" t="n">
-        <v>6.401709733077763</v>
+        <v>6.786714758642712</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1313294752310636</v>
+        <v>0.1098960540242723</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5399987567381753</v>
+        <v>-0.5405036811160893</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7546736206861493</v>
+        <v>-0.7560295187642194</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7202589934909546</v>
+        <v>-0.7218038285390519</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.001574260420065182</v>
+        <v>-0.01783771779135003</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3213750274825741</v>
+        <v>-0.3426282085309232</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.02489559107381765</v>
+        <v>-0.1038922154122621</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60.6021695000168</v>
+        <v>64.14843227219414</v>
       </c>
       <c r="B26" t="n">
-        <v>178.6813268935414</v>
+        <v>97.84668722720967</v>
       </c>
       <c r="C26" t="n">
-        <v>47.51566214768193</v>
+        <v>45.55214879691257</v>
       </c>
       <c r="D26" t="n">
-        <v>10.58227928409312</v>
+        <v>10.70850524857811</v>
       </c>
       <c r="E26" t="n">
-        <v>4.97385575700592</v>
+        <v>4.976166001657586</v>
       </c>
       <c r="F26" t="n">
-        <v>6.508537062241176</v>
+        <v>7.042974741379835</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1245974866325724</v>
+        <v>0.09897118499322974</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5586324380130377</v>
+        <v>-0.5772036692374611</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7628097650040691</v>
+        <v>-0.7720743758727714</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7352104860511569</v>
+        <v>-0.7509004717344062</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0009983754466646002</v>
+        <v>-0.04712879569322767</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3277024319507905</v>
+        <v>-0.3561132420414561</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03101966981503155</v>
+        <v>-0.01158862153612689</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61.96448805991431</v>
+        <v>65.63758778474428</v>
       </c>
       <c r="B27" t="n">
-        <v>168.0173962355696</v>
+        <v>105.5962968747998</v>
       </c>
       <c r="C27" t="n">
-        <v>47.51592130012102</v>
+        <v>45.50289872132323</v>
       </c>
       <c r="D27" t="n">
-        <v>10.56010785626019</v>
+        <v>10.68519402426334</v>
       </c>
       <c r="E27" t="n">
-        <v>4.930463648346965</v>
+        <v>2.457643954504101</v>
       </c>
       <c r="F27" t="n">
-        <v>6.699180326798351</v>
+        <v>7.263520888902794</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1147613304914998</v>
+        <v>0.09099268219491835</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5864495302255598</v>
+        <v>-0.6002660464117393</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7751110795002834</v>
+        <v>-0.7811903416849821</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.75713261747287</v>
+        <v>-0.7681304092969016</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01968870381482058</v>
+        <v>-0.01114485149890245</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.3378790465876169</v>
+        <v>-0.342667812966303</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.03100943591663051</v>
+        <v>-0.0006441602940512881</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>63.98743211572044</v>
+        <v>66.71927835882232</v>
       </c>
       <c r="B28" t="n">
-        <v>104.643716076751</v>
+        <v>96.74632661967276</v>
       </c>
       <c r="C28" t="n">
-        <v>47.73929062900439</v>
+        <v>45.51496643291079</v>
       </c>
       <c r="D28" t="n">
-        <v>10.6156504589762</v>
+        <v>10.48489651209619</v>
       </c>
       <c r="E28" t="n">
-        <v>4.709209657319743</v>
+        <v>4.549563369776806</v>
       </c>
       <c r="F28" t="n">
-        <v>7.011627532814858</v>
+        <v>7.391743949825726</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1020395631373892</v>
+        <v>0.0856189103165198</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6234532203124469</v>
+        <v>-0.6231233818961888</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7917968713341222</v>
+        <v>-0.7926874141894291</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.7855328370221364</v>
+        <v>-0.7861492264602041</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0678469749971856</v>
+        <v>-0.02146229703629968</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.352990579744257</v>
+        <v>-0.3628847229988883</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0240287719464909</v>
+        <v>-0.00332587398017628</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>64.16429914891971</v>
+        <v>68.15849774739435</v>
       </c>
       <c r="B29" t="n">
-        <v>110.3363586009672</v>
+        <v>92.98461762665464</v>
       </c>
       <c r="C29" t="n">
-        <v>47.73929062900439</v>
+        <v>45.50295160573759</v>
       </c>
       <c r="D29" t="n">
-        <v>10.62760352954224</v>
+        <v>10.12454415452533</v>
       </c>
       <c r="E29" t="n">
-        <v>4.848689950598036</v>
+        <v>4.762127787384065</v>
       </c>
       <c r="F29" t="n">
-        <v>7.040637665265462</v>
+        <v>7.546080852357866</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1010218169021378</v>
+        <v>0.07904705255869626</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6264669535241086</v>
+        <v>-0.6459698717854042</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.793173047432904</v>
+        <v>-0.8032022440309848</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7878062702794419</v>
+        <v>-0.8031849618729254</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.07285460930000763</v>
+        <v>-0.009910644782216092</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.3543117888151832</v>
+        <v>-0.3861887331054576</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0240287719464909</v>
+        <v>-0.0006559123861310523</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>66.68275224254987</v>
+        <v>69.91912515237208</v>
       </c>
       <c r="B30" t="n">
-        <v>109.5848962324168</v>
+        <v>95.91540958780048</v>
       </c>
       <c r="C30" t="n">
-        <v>46.49133470811365</v>
+        <v>45.50323886885069</v>
       </c>
       <c r="D30" t="n">
-        <v>10.48226232939735</v>
+        <v>10.44036454491993</v>
       </c>
       <c r="E30" t="n">
-        <v>4.863311141575764</v>
+        <v>2.433728192014559</v>
       </c>
       <c r="F30" t="n">
-        <v>7.390817429576907</v>
+        <v>7.89716203361802</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08766791494338268</v>
+        <v>0.07225696660937239</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6662252960796921</v>
+        <v>-0.6676998093826265</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8116653304254247</v>
+        <v>-0.8122953872416367</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8172469347456678</v>
+        <v>-0.8185530657611654</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.06545462733339692</v>
+        <v>-0.0375513767877093</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3731248090361845</v>
+        <v>-0.3731737667106511</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.04475595437556659</v>
+        <v>-0.0007197486334868664</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66.8500578728778</v>
+        <v>71.17733866283589</v>
       </c>
       <c r="B31" t="n">
-        <v>109.5848962324168</v>
+        <v>89.4053767285682</v>
       </c>
       <c r="C31" t="n">
-        <v>47.91686287249922</v>
+        <v>45.50553512705871</v>
       </c>
       <c r="D31" t="n">
-        <v>10.48226232939735</v>
+        <v>10.08734958866011</v>
       </c>
       <c r="E31" t="n">
-        <v>4.863311141575764</v>
+        <v>2.393690573869181</v>
       </c>
       <c r="F31" t="n">
-        <v>7.429860968082545</v>
+        <v>8.034128298216576</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08690919284458357</v>
+        <v>0.06761617790620002</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6686172732821144</v>
+        <v>-0.6879085438095275</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8127831614402157</v>
+        <v>-0.8229083369369543</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8189778247652666</v>
+        <v>-0.8334811255368987</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.09589403073429112</v>
+        <v>-0.02654659804793024</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3743745937609458</v>
+        <v>-0.3954842889719875</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.01765349365860816</v>
+        <v>-0.001230028235267855</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>68.03421142722161</v>
+        <v>72.35675348218656</v>
       </c>
       <c r="B32" t="n">
-        <v>161.0381516081276</v>
+        <v>89.4053767285682</v>
       </c>
       <c r="C32" t="n">
-        <v>47.52422529722317</v>
+        <v>45.50305002161299</v>
       </c>
       <c r="D32" t="n">
-        <v>10.5164308224705</v>
+        <v>10.08734958866011</v>
       </c>
       <c r="E32" t="n">
-        <v>4.056694650826427</v>
+        <v>2.401285451617123</v>
       </c>
       <c r="F32" t="n">
-        <v>7.613191462502739</v>
+        <v>8.233451139151121</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08152996681025607</v>
+        <v>0.0637560329771943</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6851337571161608</v>
+        <v>-0.7024475103762619</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8206329888867968</v>
+        <v>-0.8298917801234974</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8308465473799235</v>
+        <v>-0.8436828848935096</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.1144219218433174</v>
+        <v>-0.04864642933519497</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3832203033828507</v>
+        <v>-0.4041087598384893</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.03068151207781156</v>
+        <v>-0.0006777825806633664</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>70.24245107188362</v>
+        <v>73.8704825173198</v>
       </c>
       <c r="B33" t="n">
-        <v>184.7250883512657</v>
+        <v>92.82033035981982</v>
       </c>
       <c r="C33" t="n">
-        <v>47.53792235264847</v>
+        <v>45.5049112651704</v>
       </c>
       <c r="D33" t="n">
-        <v>9.684396548899304</v>
+        <v>10.10297847350449</v>
       </c>
       <c r="E33" t="n">
-        <v>4.995825342234109</v>
+        <v>2.546408749120235</v>
       </c>
       <c r="F33" t="n">
-        <v>7.796790364754794</v>
+        <v>8.497505941693611</v>
       </c>
       <c r="G33" t="n">
-        <v>0.07222941124281218</v>
+        <v>0.05922818368984621</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7134381465724068</v>
+        <v>-0.7169174095915346</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8344505791699822</v>
+        <v>-0.8360327268910943</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.850755645082576</v>
+        <v>-0.8533129842406815</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0004558566589738402</v>
+        <v>-0.04449697488933666</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.3997160075088947</v>
+        <v>-0.4013271879359036</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03014061701964553</v>
+        <v>-0.001091392260088031</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>71.39500048399074</v>
+        <v>74.92275906122045</v>
       </c>
       <c r="B34" t="n">
-        <v>184.7250883512657</v>
+        <v>92.82033035981982</v>
       </c>
       <c r="C34" t="n">
-        <v>48.21720709077881</v>
+        <v>45.5049112651704</v>
       </c>
       <c r="D34" t="n">
-        <v>9.684396548899304</v>
+        <v>10.10297847350449</v>
       </c>
       <c r="E34" t="n">
-        <v>4.718445777908943</v>
+        <v>2.546408749120235</v>
       </c>
       <c r="F34" t="n">
-        <v>8.002249230016103</v>
+        <v>8.681962557086365</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06816094424377574</v>
+        <v>0.05632784412806547</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7266131623169664</v>
+        <v>-0.7282876487290706</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.840923876353889</v>
+        <v>-0.8416451641401007</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8597779232262364</v>
+        <v>-0.8610698766319345</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.03707093204515306</v>
+        <v>-0.06369338672442161</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.4083256319845367</v>
+        <v>-0.4088246583111956</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.001499276870080194</v>
+        <v>-0.001091392260088031</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73.74286386070996</v>
+        <v>75.71122268994256</v>
       </c>
       <c r="B35" t="n">
-        <v>108.5594424301846</v>
+        <v>92.98396630274922</v>
       </c>
       <c r="C35" t="n">
-        <v>46.47765635826964</v>
+        <v>45.50282064615732</v>
       </c>
       <c r="D35" t="n">
-        <v>9.670799640978494</v>
+        <v>10.09137988322788</v>
       </c>
       <c r="E35" t="n">
-        <v>4.992543438699799</v>
+        <v>2.546408749120235</v>
       </c>
       <c r="F35" t="n">
-        <v>8.380049087615479</v>
+        <v>8.819414473479204</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06068721587271008</v>
+        <v>0.05427452871997403</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7510837258560439</v>
+        <v>-0.7364058922387714</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8531876034745782</v>
+        <v>-0.8456894583177156</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8761651599511689</v>
+        <v>-0.8665441186234077</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04643664978496396</v>
+        <v>-0.07591853680619913</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4258643351250024</v>
+        <v>-0.4144424616658408</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.04430037758785944</v>
+        <v>-0.0006268102571833911</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>75.46924165301336</v>
+        <v>77.89802873498492</v>
       </c>
       <c r="B36" t="n">
-        <v>101.0608705414446</v>
+        <v>103.0704882663677</v>
       </c>
       <c r="C36" t="n">
-        <v>45.21771920698517</v>
+        <v>45.50292049918971</v>
       </c>
       <c r="D36" t="n">
-        <v>9.503922528981539</v>
+        <v>9.620601236821164</v>
       </c>
       <c r="E36" t="n">
-        <v>4.932718451217488</v>
+        <v>2.45324267639382</v>
       </c>
       <c r="F36" t="n">
-        <v>8.654692260432759</v>
+        <v>9.118759826377206</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0558544926328285</v>
+        <v>0.04895838327716773</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7672191849851046</v>
+        <v>-0.7574167157692914</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8614409770160297</v>
+        <v>-0.8563567679140035</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8866905933363506</v>
+        <v>-0.8804719476371256</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.02287391111461561</v>
+        <v>-0.02746617443301806</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4387604976137293</v>
+        <v>-0.4300234547367675</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.05735828066637388</v>
+        <v>-0.0006489998199354918</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>78.48691191113794</v>
+        <v>80.46425076171982</v>
       </c>
       <c r="B37" t="n">
-        <v>192.3447997151168</v>
+        <v>95.49471449126374</v>
       </c>
       <c r="C37" t="n">
-        <v>46.51923544539069</v>
+        <v>45.50014171754761</v>
       </c>
       <c r="D37" t="n">
-        <v>9.05374575628926</v>
+        <v>9.232156392882935</v>
       </c>
       <c r="E37" t="n">
-        <v>4.893636942334986</v>
+        <v>2.559474044128925</v>
       </c>
       <c r="F37" t="n">
-        <v>9.097378675009962</v>
+        <v>9.517875398468258</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04850867210193135</v>
+        <v>0.04362045367619053</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7922199749803894</v>
+        <v>-0.7791917789859679</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8745333584552361</v>
+        <v>-0.8676278931533581</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9025329771642995</v>
+        <v>-0.8944838069366141</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.02373081568096579</v>
+        <v>-5.016836819562638e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4613027048638871</v>
+        <v>-0.4483077866772537</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.04568522789235012</v>
+        <v>-3.149278835906655e-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>80.71295541848109</v>
+        <v>80.96678304977011</v>
       </c>
       <c r="B38" t="n">
-        <v>165.8122415978793</v>
+        <v>92.82033035981982</v>
       </c>
       <c r="C38" t="n">
-        <v>46.51923544539069</v>
+        <v>45.50483277514758</v>
       </c>
       <c r="D38" t="n">
-        <v>9.05374575628926</v>
+        <v>10.10297847350449</v>
       </c>
       <c r="E38" t="n">
-        <v>4.93062590672421</v>
+        <v>2.546408749120235</v>
       </c>
       <c r="F38" t="n">
-        <v>9.511815775717709</v>
+        <v>9.79196236859887</v>
       </c>
       <c r="G38" t="n">
-        <v>0.04399382093913811</v>
+        <v>0.04288917004617637</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8082474907277889</v>
+        <v>-0.7828306233725956</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8830813613354079</v>
+        <v>-0.8694277055929793</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9123572849364311</v>
+        <v>-0.8967487175067675</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.07552895163908954</v>
+        <v>-0.1739201565124022</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.4779314050856213</v>
+        <v>-0.4518883292296121</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.04568522789235012</v>
+        <v>-0.00107395003279484</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>81.58343758953296</v>
+        <v>83.30995529067978</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1650462545115</v>
+        <v>103.277857169053</v>
       </c>
       <c r="C39" t="n">
-        <v>47.53076137301098</v>
+        <v>45.50005987716853</v>
       </c>
       <c r="D39" t="n">
-        <v>9.599023692529016</v>
+        <v>9.491412775101455</v>
       </c>
       <c r="E39" t="n">
-        <v>4.703210304760868</v>
+        <v>2.205548782682908</v>
       </c>
       <c r="F39" t="n">
-        <v>9.792247867823699</v>
+        <v>10.12001056778849</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04251096007874359</v>
+        <v>0.03872464061437341</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8139065090400966</v>
+        <v>-0.8001119032566122</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8860824616181471</v>
+        <v>-0.878631124875677</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9157487515714874</v>
+        <v>-0.9075015372324609</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.2124265085514912</v>
+        <v>-0.1125890040023228</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4844339676020488</v>
+        <v>-0.4685834314460934</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.03042340323736054</v>
+        <v>-1.330603745075543e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>83.58782410937532</v>
+        <v>85.59927980025304</v>
       </c>
       <c r="B40" t="n">
-        <v>190.0922954229752</v>
+        <v>68.29733474682625</v>
       </c>
       <c r="C40" t="n">
-        <v>47.76003479736581</v>
+        <v>46.60434865280565</v>
       </c>
       <c r="D40" t="n">
-        <v>8.360185576409615</v>
+        <v>8.21048139993292</v>
       </c>
       <c r="E40" t="n">
-        <v>4.489856687964172</v>
+        <v>2.458764933746722</v>
       </c>
       <c r="F40" t="n">
-        <v>9.9226615182383</v>
+        <v>10.35409599313745</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03882600905867416</v>
+        <v>0.03508927257764705</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8266865656730377</v>
+        <v>-0.8168631606301624</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8931868817532148</v>
+        <v>-0.8883556115284079</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9233468426441895</v>
+        <v>-0.9178027609364031</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.02053717455393168</v>
+        <v>-0.02557106721668583</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.4994068746710237</v>
+        <v>-0.2906978753223679</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.02368698359104326</v>
+        <v>-0.2454108117345907</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>85.3569214344794</v>
+        <v>88.2285287230263</v>
       </c>
       <c r="B41" t="n">
-        <v>97.54838368183134</v>
+        <v>67.84696076881886</v>
       </c>
       <c r="C41" t="n">
-        <v>47.72958240063365</v>
+        <v>45.50366470004252</v>
       </c>
       <c r="D41" t="n">
-        <v>8.394376273558541</v>
+        <v>8.619977359257215</v>
       </c>
       <c r="E41" t="n">
-        <v>4.690849081406008</v>
+        <v>4.660591193129099</v>
       </c>
       <c r="F41" t="n">
-        <v>10.27822965658895</v>
+        <v>10.93571342463499</v>
       </c>
       <c r="G41" t="n">
-        <v>0.03613540763827629</v>
+        <v>0.0316866823386476</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8367317342236015</v>
+        <v>-0.8319955223093883</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8987513094762031</v>
+        <v>-0.8966297151090743</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9291659239727685</v>
+        <v>-0.9266579539867316</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.07451437302002241</v>
+        <v>-0.105731264103204</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5126221550486021</v>
+        <v>-0.2747954539166672</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.02415230309977977</v>
+        <v>-0.0008143777872283986</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>88.28699943717245</v>
+        <v>89.58615548675823</v>
       </c>
       <c r="B42" t="n">
-        <v>176.7301920946881</v>
+        <v>67.84696076881886</v>
       </c>
       <c r="C42" t="n">
-        <v>46.51844779920611</v>
+        <v>45.50581889646626</v>
       </c>
       <c r="D42" t="n">
-        <v>8.27448539560576</v>
+        <v>8.619977359257215</v>
       </c>
       <c r="E42" t="n">
-        <v>4.839368508436767</v>
+        <v>4.176799761211901</v>
       </c>
       <c r="F42" t="n">
-        <v>10.84574025602476</v>
+        <v>11.22019669892939</v>
       </c>
       <c r="G42" t="n">
-        <v>0.03218471593735563</v>
+        <v>0.03009034411121111</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8517024467653627</v>
+        <v>-0.8378016209730151</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9072021772435794</v>
+        <v>-0.8992934686856072</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9376251172986095</v>
+        <v>-0.9298571693404957</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.1044242871713295</v>
+        <v>-0.08165891621668458</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5345100420428837</v>
+        <v>-0.5133013578431525</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.04565899422215527</v>
+        <v>-0.001293088103613144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89.05065833025692</v>
+        <v>90.91731472836719</v>
       </c>
       <c r="B43" t="n">
-        <v>106.7860968004052</v>
+        <v>58.54627075915572</v>
       </c>
       <c r="C43" t="n">
-        <v>46.3178257348947</v>
+        <v>45.50375067087761</v>
       </c>
       <c r="D43" t="n">
-        <v>8.2697783359861</v>
+        <v>7.930133240828324</v>
       </c>
       <c r="E43" t="n">
-        <v>4.916597752597037</v>
+        <v>2.568062420659474</v>
       </c>
       <c r="F43" t="n">
-        <v>11.00121318640335</v>
+        <v>11.36193111220799</v>
       </c>
       <c r="G43" t="n">
-        <v>0.03125645770291891</v>
+        <v>0.02854428848228721</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.8552851695847266</v>
+        <v>-0.845802725052212</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.9092497276723043</v>
+        <v>-0.9043541817743941</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.9396090722242576</v>
+        <v>-0.9345210170376774</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.1209109327565905</v>
+        <v>-0.09587743501742009</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5402146272241136</v>
+        <v>-0.06024969510408873</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0425261160207808</v>
+        <v>-0.0008334824172466504</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>90.14715904711929</v>
+        <v>91.85341746204823</v>
       </c>
       <c r="B44" t="n">
-        <v>97.54838368183134</v>
+        <v>58.54627075915572</v>
       </c>
       <c r="C44" t="n">
-        <v>47.88446217947823</v>
+        <v>45.50378406821687</v>
       </c>
       <c r="D44" t="n">
-        <v>8.394376273558541</v>
+        <v>7.930133240828324</v>
       </c>
       <c r="E44" t="n">
-        <v>4.690849081406008</v>
+        <v>2.551340082783853</v>
       </c>
       <c r="F44" t="n">
-        <v>11.26709905004246</v>
+        <v>11.56349553233127</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03001217665815449</v>
+        <v>0.02758050327857178</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.8601900495971431</v>
+        <v>-0.8502217617530198</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.9120560429899437</v>
+        <v>-0.9068499464831326</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9422965719089001</v>
+        <v>-0.9369885426700691</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2033473394201358</v>
+        <v>-0.1249768313494238</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5484055640380051</v>
+        <v>-0.0196852433112434</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.01890001316718364</v>
+        <v>-0.0008409040481949237</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>91.12187542906798</v>
+        <v>92.90432751735298</v>
       </c>
       <c r="B45" t="n">
-        <v>190.0922954229752</v>
+        <v>58.54627075915572</v>
       </c>
       <c r="C45" t="n">
-        <v>45.41118041761413</v>
+        <v>45.50324153829244</v>
       </c>
       <c r="D45" t="n">
-        <v>8.360185576409615</v>
+        <v>8.526502535853067</v>
       </c>
       <c r="E45" t="n">
-        <v>4.489856687964172</v>
+        <v>2.414688212654994</v>
       </c>
       <c r="F45" t="n">
-        <v>11.46598801853692</v>
+        <v>11.91433528905847</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02893840057294355</v>
+        <v>0.02661744016366073</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8643884503893743</v>
+        <v>-0.8549377939632475</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9144891606462198</v>
+        <v>-0.9095144715544597</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9445754954663992</v>
+        <v>-0.9395923202180418</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1805010653571101</v>
+        <v>-0.2086888576468969</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.555686763378077</v>
+        <v>-0.07737283815620741</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.05362199503809851</v>
+        <v>-0.0007203418427650932</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>93.44905853813783</v>
+        <v>94.59764282044904</v>
       </c>
       <c r="B46" t="n">
-        <v>97.54822553258869</v>
+        <v>88.81760954547771</v>
       </c>
       <c r="C46" t="n">
-        <v>46.47296935146557</v>
+        <v>45.50012128233234</v>
       </c>
       <c r="D46" t="n">
-        <v>7.793507198191063</v>
+        <v>7.728079635545914</v>
       </c>
       <c r="E46" t="n">
-        <v>4.690849081406008</v>
+        <v>2.545882243869944</v>
       </c>
       <c r="F46" t="n">
-        <v>11.84066636560236</v>
+        <v>12.1247838657163</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0265210529849137</v>
+        <v>0.02498160123965914</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8738030671164909</v>
+        <v>-0.8611877262666334</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9200395740364973</v>
+        <v>-0.9126550783620813</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9496084306607174</v>
+        <v>-0.9429164537683665</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1517405496117375</v>
+        <v>-0.01363534370073815</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.5730709834771682</v>
+        <v>-0.5490082050956994</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.04414427019712121</v>
+        <v>-2.695162940991036e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>95.2241383963368</v>
+        <v>96.35203350434229</v>
       </c>
       <c r="B47" t="n">
-        <v>76.53256142202716</v>
+        <v>98.50529303300785</v>
       </c>
       <c r="C47" t="n">
-        <v>46.4974450150108</v>
+        <v>45.5248981238804</v>
       </c>
       <c r="D47" t="n">
-        <v>7.459684963929247</v>
+        <v>7.459475780632736</v>
       </c>
       <c r="E47" t="n">
-        <v>3.463788210995948</v>
+        <v>2.545566433681712</v>
       </c>
       <c r="F47" t="n">
-        <v>12.16340838523251</v>
+        <v>12.46528174964168</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02487704655932538</v>
+        <v>0.02348381216818173</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8803606393276943</v>
+        <v>-0.8682560293290777</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.9239451852864426</v>
+        <v>-0.9167801860697242</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9530407241130425</v>
+        <v>-0.9467277045583767</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1355064760183101</v>
+        <v>-0.0005344586033748125</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5863309537941271</v>
+        <v>-0.5615082387184388</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.04495946678896852</v>
+        <v>-0.005532916417866629</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>97.36240147091242</v>
+        <v>97.0142062303637</v>
       </c>
       <c r="B48" t="n">
-        <v>106.7419691064762</v>
+        <v>91.15989832348927</v>
       </c>
       <c r="C48" t="n">
-        <v>42.78788655677219</v>
+        <v>45.5248981238804</v>
       </c>
       <c r="D48" t="n">
-        <v>7.069895682774661</v>
+        <v>7.459475780632736</v>
       </c>
       <c r="E48" t="n">
-        <v>4.678263825834765</v>
+        <v>2.182013849014484</v>
       </c>
       <c r="F48" t="n">
-        <v>12.55345274829672</v>
+        <v>12.61612750048459</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02307627617815243</v>
+        <v>0.0229598342232763</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.88764683930118</v>
+        <v>-0.8707782814589931</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9283251287389337</v>
+        <v>-0.9182561265379202</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9567831170575072</v>
+        <v>-0.9480704746797755</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.04314602038316288</v>
+        <v>-0.0226190370215109</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.6023039280621636</v>
+        <v>-0.5662262193913414</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.09294887843280884</v>
+        <v>-0.005532916417866629</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>97.36240147091242</v>
+        <v>98.41420292218217</v>
       </c>
       <c r="B49" t="n">
-        <v>106.7419691064762</v>
+        <v>69.92771637746554</v>
       </c>
       <c r="C49" t="n">
-        <v>42.78788655677219</v>
+        <v>45.95969355918146</v>
       </c>
       <c r="D49" t="n">
-        <v>7.069895682774661</v>
+        <v>7.267131644020009</v>
       </c>
       <c r="E49" t="n">
-        <v>4.718365330381118</v>
+        <v>4.717086789939435</v>
       </c>
       <c r="F49" t="n">
-        <v>12.55345274829672</v>
+        <v>12.9132685854318</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02307627617815243</v>
+        <v>0.02189465890982811</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.88764683930118</v>
+        <v>-0.8759103757527226</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9283251287389337</v>
+        <v>-0.9212859907095015</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9567831170575072</v>
+        <v>-0.9507777529409727</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.04314602038316288</v>
+        <v>-0.02868325352754777</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6023039280621636</v>
+        <v>-0.5762011958205479</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.09294887843280884</v>
+        <v>-0.1021541242625464</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99.67984140523392</v>
+        <v>99.99999991074807</v>
       </c>
       <c r="B50" t="n">
-        <v>199.7095618097653</v>
+        <v>81.00917471215348</v>
       </c>
       <c r="C50" t="n">
-        <v>47.5890866910422</v>
+        <v>45.50002979171688</v>
       </c>
       <c r="D50" t="n">
-        <v>6.225681476883455</v>
+        <v>6.990614444103101</v>
       </c>
       <c r="E50" t="n">
-        <v>4.694675902020389</v>
+        <v>4.527236811674377</v>
       </c>
       <c r="F50" t="n">
-        <v>12.92404369297802</v>
+        <v>13.21230167454317</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02130196913426158</v>
+        <v>0.02075487826124938</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8948894846239291</v>
+        <v>-0.8814124036699688</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9326108881668534</v>
+        <v>-0.9245756804477259</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9604275869098997</v>
+        <v>-0.9536420782657697</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.00169933023616462</v>
+        <v>-0.0001553769469673069</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6196153659664938</v>
+        <v>-0.5874999993640799</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.02812014349944854</v>
+        <v>-6.620381528543717e-06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>99.99999925936223</v>
+        <v>99.99999991074807</v>
       </c>
       <c r="B51" t="n">
-        <v>77.77350935272921</v>
+        <v>81.23265539708035</v>
       </c>
       <c r="C51" t="n">
-        <v>46.30576072396562</v>
+        <v>45.50002979171688</v>
       </c>
       <c r="D51" t="n">
-        <v>6.266787406475838</v>
+        <v>6.990614444103101</v>
       </c>
       <c r="E51" t="n">
-        <v>4.952855862114075</v>
+        <v>4.527236811674377</v>
       </c>
       <c r="F51" t="n">
-        <v>13.00321773644441</v>
+        <v>13.21230167454317</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02108274498322751</v>
+        <v>0.02075487826124938</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8958233575958496</v>
+        <v>-0.8814124036699688</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9331490069773587</v>
+        <v>-0.9245756804477259</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9608904523763487</v>
+        <v>-0.9536420782657697</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.003114839821079732</v>
+        <v>-0.0001553769469673069</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.6220069674614203</v>
+        <v>-0.5874999993640799</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.04241952821539687</v>
+        <v>-6.620381528543717e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3632,13 +3892,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.016335833673474</v>
+        <v>1.018059711963271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01286563888365776</v>
+        <v>0.01501222490706126</v>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -3656,13 +3916,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.055540299472449</v>
+        <v>1.040520970008332</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01750196226366884</v>
+        <v>0.01597531738519873</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -3680,13 +3940,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.074638481929538</v>
+        <v>1.070163322244104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01637163620132307</v>
+        <v>0.01687976082945814</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -3704,13 +3964,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.087765202189502</v>
+        <v>1.096311343413006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01719156443747046</v>
+        <v>0.01707114005747117</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -3728,13 +3988,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.095342026488169</v>
+        <v>1.105111715313105</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01544270741236993</v>
+        <v>0.01581694946933513</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -3752,13 +4012,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9734733849760484</v>
+        <v>0.971997678647666</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01584224716750841</v>
+        <v>0.01807130343693958</v>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -3776,13 +4036,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.040361703566819</v>
+        <v>1.022778112338953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01213311923732303</v>
+        <v>0.016480202955242</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -3800,13 +4060,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.058543014543942</v>
+        <v>1.045173712461652</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01697534273814133</v>
+        <v>0.01576547917892208</v>
       </c>
       <c r="F9" t="n">
-        <v>204</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -3824,13 +4084,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.067202920261504</v>
+        <v>1.040299829550457</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0150968547146876</v>
+        <v>0.01842393374313767</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3848,13 +4108,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.082412038795332</v>
+        <v>1.082447408351658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01780344148477744</v>
+        <v>0.01458613379903277</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -3872,13 +4132,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9516395220384712</v>
+        <v>0.9072337919198168</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01571347733476325</v>
+        <v>0.01359963992328862</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -3896,13 +4156,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9845522398301844</v>
+        <v>0.9908585728504083</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01673395989354442</v>
+        <v>0.0202627413557166</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -3920,13 +4180,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.009838095169294</v>
+        <v>1.017388219165847</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01611390364593702</v>
+        <v>0.01731653547070015</v>
       </c>
       <c r="F14" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3944,13 +4204,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.03326867321689</v>
+        <v>1.041579844565503</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01726019430346071</v>
+        <v>0.01953937885845601</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3968,13 +4228,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.071641122532322</v>
+        <v>1.03613784696387</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01846129808407851</v>
+        <v>0.01655993733448832</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -3992,13 +4252,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9148418007460164</v>
+        <v>0.8899747472907035</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01472435846613143</v>
+        <v>0.01734151686131722</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
@@ -4016,13 +4276,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9778706452800108</v>
+        <v>0.9642870688097008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0181722168710621</v>
+        <v>0.01561196246552961</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -4040,13 +4300,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.010070554004106</v>
+        <v>1.023626759890535</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01659726359494764</v>
+        <v>0.01816429919380777</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
@@ -4064,13 +4324,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.046719805418819</v>
+        <v>1.020229012842055</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01714704299892776</v>
+        <v>0.01736423740810522</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
@@ -4088,13 +4348,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.029948050981216</v>
+        <v>1.02435234879514</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0168338794809651</v>
+        <v>0.01478466586076552</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4322,31 +4582,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>66.61</v>
+        <v>68.84</v>
       </c>
       <c r="D2" t="n">
-        <v>17.61</v>
+        <v>17.14</v>
       </c>
       <c r="E2" t="n">
-        <v>26.43</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>45.69</v>
+        <v>47.78</v>
       </c>
       <c r="G2" t="n">
-        <v>50.94</v>
+        <v>54.49</v>
       </c>
       <c r="H2" t="n">
-        <v>61.28</v>
+        <v>64.89</v>
       </c>
       <c r="I2" t="n">
-        <v>81.37</v>
+        <v>82.72</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>54.31</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="3">
@@ -4359,31 +4619,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>46.78</v>
+        <v>45.58</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.49</v>
+        <v>0.44</v>
       </c>
       <c r="F3" t="n">
-        <v>42.79</v>
+        <v>45.5</v>
       </c>
       <c r="G3" t="n">
-        <v>46.48</v>
+        <v>45.5</v>
       </c>
       <c r="H3" t="n">
-        <v>46.52</v>
+        <v>45.5</v>
       </c>
       <c r="I3" t="n">
-        <v>47.64</v>
+        <v>45.51</v>
       </c>
       <c r="J3" t="n">
-        <v>48.22</v>
+        <v>46.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -4396,31 +4656,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.539999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="E4" t="n">
-        <v>18.57</v>
+        <v>17.92</v>
       </c>
       <c r="F4" t="n">
-        <v>6.23</v>
+        <v>6.99</v>
       </c>
       <c r="G4" t="n">
-        <v>7.14</v>
+        <v>7.34</v>
       </c>
       <c r="H4" t="n">
-        <v>8.27</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28</v>
+        <v>10.68</v>
       </c>
       <c r="J4" t="n">
-        <v>11.31</v>
+        <v>11.39</v>
       </c>
       <c r="K4" t="n">
-        <v>5.09</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -4433,31 +4693,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>129.58</v>
+        <v>87.64</v>
       </c>
       <c r="D5" t="n">
-        <v>43.96</v>
+        <v>17.9</v>
       </c>
       <c r="E5" t="n">
-        <v>33.92</v>
+        <v>20.43</v>
       </c>
       <c r="F5" t="n">
-        <v>68.88</v>
+        <v>58.55</v>
       </c>
       <c r="G5" t="n">
-        <v>97.59</v>
+        <v>69.5</v>
       </c>
       <c r="H5" t="n">
-        <v>107.16</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>183.21</v>
+        <v>103.23</v>
       </c>
       <c r="J5" t="n">
-        <v>199.71</v>
+        <v>120.72</v>
       </c>
       <c r="K5" t="n">
-        <v>130.83</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="6">
@@ -4470,31 +4730,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.64</v>
+        <v>3.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>1.14</v>
       </c>
       <c r="E6" t="n">
-        <v>7.88</v>
+        <v>33.14</v>
       </c>
       <c r="F6" t="n">
-        <v>3.46</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>4.64</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>4.71</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="K6" t="n">
-        <v>1.53</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -4508,183 +4768,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>delta_ratio_alvo</t>
+          <t>rho_pct</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>V(rho=0.0)</t>
+          <t>V_min_m3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>delta_real(rho=0.0)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>V(rho=2.5)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta_real(rho=2.5)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>V(rho=5.0)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>delta_real(rho=5.0)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>V(rho=10.0)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>delta_real(rho=10.0)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>delta%(rho=2.5)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>delta%(rho=5.0)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>delta%(rho=10.0)</t>
+          <t>delta_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.09986111459225167</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.070983467350363</v>
+        <v>4.799745923264973</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09904609550456385</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7.017485609468582</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.09826311493478422</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7.040637665265462</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.1010218169021378</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.972384963246599</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.1007389611596942</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.7565829863526403</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.4291595677605565</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1.394410050016859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1780579677198307</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>5.923580145607824</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1813709725151324</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5.832387392946071</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1822489960495012</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.911884437455</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1807387035947317</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.911094329046179</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.1747913047871907</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-1.539487107798649</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.1974432330673537</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.2107815924614901</v>
+        <v>6.041808869596619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.2562548208474097</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>5.273338404600723</v>
+        <v>5.413971686785674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25306379657663</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.30328693711793</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.257815405715495</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.25487552501313</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2529622334716599</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.283935387656005</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.2523727629987129</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5679235850117018</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.3501174810151494</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2009539734077521</v>
+        <v>12.79704745502197</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5.787501461115749</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20.57932969041134</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6.090634014927824</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26.89492552940676</v>
       </c>
     </row>
   </sheetData>
